--- a/RegistrarOrdenDePreparacion/planilla RegistrarOrdenDePreparación.xlsx
+++ b/RegistrarOrdenDePreparacion/planilla RegistrarOrdenDePreparación.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\C#\CAI\GrupoC\RegistrarOrdenDePreparacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622FC05E-0298-430B-BA0C-E3066FDA88FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E988EA4-092F-4149-99B6-E647A2E5ABB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="88">
   <si>
     <t>NOMBRE PROTOTIPO: CU4 - Registrar Orden de Preparación</t>
   </si>
@@ -263,13 +263,43 @@
   </si>
   <si>
     <t>Sección "Datos del transportista autorizado a retirar". El campo no admite más de 8 caracteres. No se valida que sea un DNI válido en la pantalla en sí.</t>
+  </si>
+  <si>
+    <t>Agregar a la Orden</t>
+  </si>
+  <si>
+    <t>Boton</t>
+  </si>
+  <si>
+    <t>Al precionar valida que haya un producto seleccionado y una cantidad escrita.</t>
+  </si>
+  <si>
+    <t>"Error: seleccione un producto e ingrese una cantidad mayor a cero".</t>
+  </si>
+  <si>
+    <t>Es el disparador de todas las validaciones de los campos 3, 4 y 5.</t>
+  </si>
+  <si>
+    <t>Cancelar</t>
+  </si>
+  <si>
+    <t>Cierra la pantalla sin validar ni preguntar nada.</t>
+  </si>
+  <si>
+    <t>Confirmar Orden</t>
+  </si>
+  <si>
+    <t>Valida que todos los campos obligatorios estén llenos.</t>
+  </si>
+  <si>
+    <t>Adicionalmente de confirmar la orden, si fue exitosa dispara la validación de stock mínimo.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,6 +340,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -397,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -406,19 +442,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -429,23 +453,51 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -750,111 +802,113 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="17.140625" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" customWidth="1"/>
-    <col min="9" max="9" width="22.140625" customWidth="1"/>
-    <col min="10" max="10" width="29.42578125" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="2"/>
+    <col min="5" max="5" width="20.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="22.140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="29.42578125" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="9"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="12"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="5" t="s">
         <v>22</v>
       </c>
     </row>
@@ -862,7 +916,7 @@
       <c r="A5" s="13">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="13" t="s">
@@ -871,22 +925,22 @@
       <c r="D5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="15" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -894,7 +948,7 @@
       <c r="A6" s="13">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="14" t="s">
         <v>30</v>
       </c>
       <c r="C6" s="13" t="s">
@@ -903,22 +957,22 @@
       <c r="D6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="15" t="s">
         <v>26</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="16" t="s">
         <v>35</v>
       </c>
     </row>
@@ -926,7 +980,7 @@
       <c r="A7" s="13">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="14" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="13" t="s">
@@ -935,22 +989,22 @@
       <c r="D7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="15" t="s">
         <v>26</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="16" t="s">
         <v>38</v>
       </c>
     </row>
@@ -958,7 +1012,7 @@
       <c r="A8" s="13">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -967,22 +1021,22 @@
       <c r="D8" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="15" t="s">
         <v>26</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="16" t="s">
         <v>69</v>
       </c>
     </row>
@@ -990,7 +1044,7 @@
       <c r="A9" s="13">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C9" s="13" t="s">
@@ -999,93 +1053,93 @@
       <c r="D9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="15" t="s">
         <v>45</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="16" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="13">
+    <row r="10" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="13">
-        <v>30</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="13">
+        <v>30</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
+        <v>8</v>
+      </c>
+      <c r="B12" s="14" t="s">
         <v>52</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A12" s="13">
-        <v>8</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>57</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>53</v>
@@ -1093,22 +1147,22 @@
       <c r="D12" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="15" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="16" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1116,8 +1170,8 @@
       <c r="A13" s="13">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>58</v>
+      <c r="B13" s="14" t="s">
+        <v>57</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>53</v>
@@ -1125,87 +1179,183 @@
       <c r="D13" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="15" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
+        <v>10</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I14" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J14" s="16" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="13">
-        <v>10</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="13">
-        <v>8</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="13">
+        <v>8</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
+        <v>12</v>
+      </c>
+      <c r="B16" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C16" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D16" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="14" t="s">
+      <c r="E16" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H16" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I16" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J16" s="16" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="20">
+        <v>13</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="20">
+        <v>14</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1213,7 +1363,7 @@
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
